--- a/data/raw/inventory/Week 27/Tonor/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 27/Tonor/Seller FBA Inventory (SP-API).xlsx
@@ -1887,7 +1887,7 @@
         <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
         <v>4</v>
